--- a/multi_regression/results_n_10_m_1000_d_10/figs_100/regression_result.xlsx
+++ b/multi_regression/results_n_10_m_1000_d_10/figs_100/regression_result.xlsx
@@ -549,12 +549,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1795.4261 $\pm$ 2408.5153</t>
+          <t>2032.3962 $\pm$ 2421.6675</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3899.6974 $\pm$ 2496.5135</t>
+          <t>3652.4886 $\pm$ 2702.2815</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
